--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" s="15">
         <v>8</v>
       </c>
       <c r="K16" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="14">
-        <v>-58.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="14">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.848484848484</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,37 +975,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-83.333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J17" s="15">
         <v>13</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L17" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M17" s="14">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="N17" s="14">
         <v>-50</v>
@@ -1016,81 +1016,81 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K18" s="14">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M18" s="14">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N18" s="14">
-        <v>-85.106382978723</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>2</v>
+      <c r="C19" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F19" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
-        <v>-20</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I19" s="15">
         <v>19</v>
       </c>
       <c r="J19" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.523809523809</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-5</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>-26.923076923076</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-29.629629629629</v>
+        <v>-42.424242424242</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1131,7 +1131,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.916666666666</v>
+        <v>-98.148148148148</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G21" s="17">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.555555555555</v>
+        <v>-3.125</v>
       </c>
       <c r="I21" s="17">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J21" s="17">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.689655172413</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.363636363636</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.333333333333</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.725274725274</v>
+        <v>-75.728155339805</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,35 +1223,35 @@
       <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-50</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>62.5</v>
+        <v>120</v>
       </c>
       <c r="I23" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="15">
         <v>12</v>
       </c>
       <c r="K23" s="14">
-        <v>33.333333333333</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>45.454545454545</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M23" s="14">
-        <v>220</v>
+        <v>183.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="15">
         <v>23</v>
       </c>
       <c r="G24" s="15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H24" s="14">
-        <v>-45.238095238095</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I24" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J24" s="15">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.076923076923</v>
+        <v>-22.033898305084</v>
       </c>
       <c r="L24" s="14">
-        <v>-4.761904761904</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M24" s="14">
-        <v>-20</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1315,22 +1315,22 @@
         <v>4</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H25" s="14">
-        <v>-81.818181818181</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="I25" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K25" s="14">
-        <v>-58.333333333333</v>
+        <v>-59.259259259259</v>
       </c>
       <c r="L25" s="14">
-        <v>-37.5</v>
+        <v>-31.25</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>500</v>
       </c>
       <c r="F26" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H26" s="14">
-        <v>-52.941176470588</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J26" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K26" s="14">
-        <v>-34.782608695652</v>
+        <v>-12.5</v>
       </c>
       <c r="L26" s="14">
-        <v>66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="M26" s="14">
-        <v>-51.612903225806</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,8 +1434,8 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="15">
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1444,16 +1444,16 @@
         <v>21</v>
       </c>
       <c r="I28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="15">
         <v>1</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -933,8 +933,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -943,31 +943,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
+        <v>4</v>
+      </c>
+      <c r="G16" s="15">
         <v>3</v>
       </c>
-      <c r="G16" s="15">
-        <v>4</v>
-      </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16" s="15">
         <v>8</v>
       </c>
       <c r="K16" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N16" s="14">
-        <v>-83.333333333333</v>
+        <v>-82.608695652173</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,7 +975,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -984,31 +984,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
         <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I17" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15">
         <v>13</v>
       </c>
       <c r="K17" s="14">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L17" s="14">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M17" s="14">
-        <v>87.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N17" s="14">
-        <v>-50</v>
+        <v>-54.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
+        <v>7</v>
+      </c>
+      <c r="G18" s="15">
         <v>5</v>
       </c>
-      <c r="G18" s="15">
-        <v>4</v>
-      </c>
       <c r="H18" s="14">
+        <v>40</v>
+      </c>
+      <c r="I18" s="15">
+        <v>10</v>
+      </c>
+      <c r="J18" s="15">
+        <v>12</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L18" s="14">
         <v>25</v>
       </c>
-      <c r="I18" s="15">
-        <v>8</v>
-      </c>
-      <c r="J18" s="15">
-        <v>11</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-27.272727272727</v>
-      </c>
-      <c r="L18" s="14">
-        <v>14.285714285714</v>
-      </c>
       <c r="M18" s="14">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N18" s="14">
-        <v>-84.615384615384</v>
+        <v>-83.870967741935</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>20</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14">
         <v>-100</v>
       </c>
       <c r="F19" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G19" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>-46.666666666666</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I19" s="15">
         <v>19</v>
       </c>
       <c r="J19" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" s="14">
-        <v>-20.833333333333</v>
+        <v>-24</v>
       </c>
       <c r="L19" s="14">
-        <v>-20.833333333333</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M19" s="14">
-        <v>-36.666666666666</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.424242424242</v>
+        <v>-48.648648648648</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M20" s="14">
         <v>-83.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.148148148148</v>
+        <v>-98.214285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
+        <v>25</v>
+      </c>
+      <c r="G21" s="17">
         <v>31</v>
       </c>
-      <c r="G21" s="17">
-        <v>32</v>
-      </c>
       <c r="H21" s="18">
-        <v>-3.125</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I21" s="17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J21" s="17">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.354838709677</v>
+        <v>-14.0625</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.634920634920</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.470588235294</v>
+        <v>-25.675675675675</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.728155339805</v>
+        <v>-76.793248945147</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
         <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I23" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" s="15">
         <v>12</v>
       </c>
       <c r="K23" s="14">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L23" s="14">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="M23" s="14">
-        <v>183.333333333333</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>-14.285714285714</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="15">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G24" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.352941176470</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="I24" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J24" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.033898305084</v>
+        <v>-26.865671641791</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.127659574468</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="M24" s="14">
-        <v>-11.538461538461</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>-78.947368421052</v>
+        <v>-76.190476190476</v>
       </c>
       <c r="I25" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J25" s="15">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K25" s="14">
-        <v>-59.259259259259</v>
+        <v>-62.857142857142</v>
       </c>
       <c r="L25" s="14">
-        <v>-31.25</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J26" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.5</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L26" s="14">
-        <v>75</v>
+        <v>108.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-36.363636363636</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>-100</v>
       </c>
       <c r="M29" s="14">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>-100</v>
       </c>
       <c r="M30" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -936,70 +936,70 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-56.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-27.272727272727</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-82.608695652173</v>
+        <v>-87.037037037037</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="14">
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G17" s="15">
         <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>42.857142857142</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I17" s="15">
         <v>16</v>
       </c>
       <c r="J17" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="14">
-        <v>23.076923076923</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L17" s="14">
         <v>23.076923076923</v>
@@ -1008,7 +1008,7 @@
         <v>77.777777777777</v>
       </c>
       <c r="N17" s="14">
-        <v>-54.285714285714</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,89 +1016,89 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>8</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F18" s="15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="I18" s="15">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>-16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L18" s="14">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-28.571428571428</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N18" s="14">
-        <v>-83.870967741935</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
+      <c r="C19" s="15">
+        <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" s="15">
         <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>-78.571428571428</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I19" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J19" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K19" s="14">
-        <v>-24</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.923076923076</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M19" s="14">
-        <v>-42.424242424242</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="N19" s="14">
-        <v>-48.648648648648</v>
+        <v>-43.902439024390</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,32 +1106,32 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+      <c r="F20" s="15">
+        <v>1</v>
       </c>
       <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <v>2</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="15">
-        <v>1</v>
       </c>
       <c r="J20" s="15">
         <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="M20" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.214285714285</v>
+        <v>-96.774193548387</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G21" s="17">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.354838709677</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I21" s="17">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J21" s="17">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.0625</v>
+        <v>-8.219178082191</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.428571428571</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.675675675675</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.793248945147</v>
+        <v>-75.185185185185</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
         <v>18</v>
       </c>
       <c r="J23" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" s="14">
-        <v>50</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L23" s="14">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="M23" s="14">
         <v>157.142857142857</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.5</v>
+        <v>-75</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G24" s="15">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H24" s="14">
-        <v>-39.393939393939</v>
+        <v>-56.097560975609</v>
       </c>
       <c r="I24" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J24" s="15">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.865671641791</v>
+        <v>-36.144578313253</v>
       </c>
       <c r="L24" s="14">
-        <v>-9.259259259259</v>
+        <v>-27.397260273972</v>
       </c>
       <c r="M24" s="14">
-        <v>-19.672131147541</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
+        <v>-80</v>
+      </c>
+      <c r="F25" s="15">
+        <v>6</v>
+      </c>
+      <c r="G25" s="15">
+        <v>24</v>
+      </c>
+      <c r="H25" s="14">
         <v>-75</v>
       </c>
-      <c r="F25" s="15">
-        <v>5</v>
-      </c>
-      <c r="G25" s="15">
-        <v>21</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-76.190476190476</v>
-      </c>
       <c r="I25" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J25" s="15">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K25" s="14">
-        <v>-62.857142857142</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>-27.777777777777</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-62.5</v>
       </c>
       <c r="F26" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I26" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J26" s="15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K26" s="14">
-        <v>-10.714285714285</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L26" s="14">
-        <v>108.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M26" s="14">
-        <v>-30.555555555555</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1428,29 +1428,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>2</v>
       </c>
       <c r="J28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -922,11 +922,11 @@
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="14">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14">
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,20 +936,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>3</v>
-      </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
         <v>7</v>
@@ -964,51 +964,51 @@
         <v>-56.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.037037037037</v>
+        <v>-87.931034482758</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>1</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>4</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14">
-        <v>-42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="I17" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" s="14">
-        <v>14.285714285714</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>23.076923076923</v>
+        <v>6.25</v>
       </c>
       <c r="M17" s="14">
-        <v>77.777777777777</v>
+        <v>70</v>
       </c>
       <c r="N17" s="14">
-        <v>-60</v>
+        <v>-61.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>8</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
         <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>28.571428571428</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L18" s="14">
-        <v>28.571428571428</v>
+        <v>26.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>5.882352941176</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="N18" s="14">
-        <v>-75</v>
+        <v>-76.25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G19" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" s="14">
-        <v>-57.142857142857</v>
+        <v>-31.25</v>
       </c>
       <c r="I19" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J19" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K19" s="14">
-        <v>-23.333333333333</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.857142857142</v>
+        <v>0</v>
       </c>
       <c r="M19" s="14">
-        <v>-32.352941176470</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N19" s="14">
-        <v>-43.902439024390</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1109,11 +1109,11 @@
       <c r="F20" s="15">
         <v>1</v>
       </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="14">
-        <v>0</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="15">
         <v>2</v>
@@ -1125,13 +1125,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M20" s="14">
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.774193548387</v>
+        <v>-96.969696969697</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>44.444444444444</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H21" s="18">
-        <v>7.142857142857</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I21" s="17">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J21" s="17">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.219178082191</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.189873417721</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.189873417721</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.185185185185</v>
+        <v>-74.061433447099</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,26 +1182,26 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-100</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14">
         <v>-100</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
         <v>3</v>
       </c>
       <c r="G23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="14">
-        <v>38.461538461538</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L23" s="14">
-        <v>12.5</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M23" s="14">
-        <v>157.142857142857</v>
+        <v>137.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-75</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F24" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H24" s="14">
-        <v>-56.097560975609</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="I24" s="15">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J24" s="15">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K24" s="14">
-        <v>-36.144578313253</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.397260273972</v>
+        <v>-26.582278481012</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.461538461538</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H25" s="14">
-        <v>-75</v>
+        <v>-76.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J25" s="15">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.666666666666</v>
+        <v>-68.518518518518</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.782608695652</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
+        <v>14</v>
+      </c>
+      <c r="G26" s="15">
         <v>15</v>
       </c>
-      <c r="G26" s="15">
-        <v>17</v>
-      </c>
       <c r="H26" s="14">
-        <v>-11.764705882352</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J26" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14">
-        <v>-22.222222222222</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="L26" s="14">
-        <v>100</v>
+        <v>61.111111111111</v>
       </c>
       <c r="M26" s="14">
-        <v>-28.205128205128</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
         <v>2</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>1</v>
       </c>
       <c r="G16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K16" s="14">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L16" s="14">
-        <v>-56.25</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.931034482758</v>
+        <v>-87.692307692307</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F17" s="15">
+        <v>3</v>
+      </c>
+      <c r="G17" s="15">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>-40</v>
+      </c>
+      <c r="I17" s="15">
+        <v>18</v>
+      </c>
+      <c r="J17" s="15">
+        <v>18</v>
+      </c>
+      <c r="K17" s="14">
         <v>0</v>
       </c>
-      <c r="F17" s="15">
-        <v>4</v>
-      </c>
-      <c r="G17" s="15">
-        <v>2</v>
-      </c>
-      <c r="H17" s="14">
-        <v>100</v>
-      </c>
-      <c r="I17" s="15">
-        <v>17</v>
-      </c>
-      <c r="J17" s="15">
-        <v>15</v>
-      </c>
-      <c r="K17" s="14">
-        <v>13.333333333333</v>
-      </c>
       <c r="L17" s="14">
-        <v>6.25</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M17" s="14">
-        <v>70</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N17" s="14">
-        <v>-61.363636363636</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I18" s="15">
         <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="14">
-        <v>35.714285714285</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>26.666666666666</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M18" s="14">
-        <v>-9.523809523809</v>
+        <v>-24</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.25</v>
+        <v>-76.829268292682</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>200</v>
       </c>
       <c r="F19" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>-31.25</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J19" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K19" s="14">
-        <v>-18.918918918918</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="L19" s="14">
         <v>0</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.285714285714</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.571428571428</v>
+        <v>-29.787234042553</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G20" s="15">
+        <v>2</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-80</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M20" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.969696969697</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G21" s="17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H21" s="18">
-        <v>26.086956521739</v>
+        <v>10.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J21" s="17">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.172839506172</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.643678160919</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.636363636363</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.061433447099</v>
+        <v>-74.534161490683</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1201,7 +1201,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
         <v>-100</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>50</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="15">
         <v>19</v>
       </c>
       <c r="J23" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>35.714285714285</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L23" s="14">
-        <v>11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>137.5</v>
+        <v>90</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-61.538461538461</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H24" s="14">
-        <v>-56.818181818181</v>
+        <v>-59.183673469387</v>
       </c>
       <c r="I24" s="15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J24" s="15">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K24" s="14">
-        <v>-39.583333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L24" s="14">
-        <v>-26.582278481012</v>
+        <v>-30</v>
       </c>
       <c r="M24" s="14">
-        <v>-21.621621621621</v>
+        <v>-21.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
+        <v>4</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F25" s="15">
         <v>9</v>
       </c>
-      <c r="E25" s="14">
-        <v>-77.777777777777</v>
-      </c>
-      <c r="F25" s="15">
-        <v>7</v>
-      </c>
       <c r="G25" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H25" s="14">
-        <v>-76.666666666666</v>
+        <v>-70.967741935483</v>
       </c>
       <c r="I25" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J25" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K25" s="14">
-        <v>-68.518518518518</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.615384615384</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
         <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G26" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.666666666666</v>
+        <v>-45</v>
       </c>
       <c r="I26" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J26" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K26" s="14">
-        <v>-23.684210526315</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L26" s="14">
-        <v>61.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-34.090909090909</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,13 +1435,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>3</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="15">
+        <v>1</v>
+      </c>
+      <c r="K29" s="14">
+        <v>-100</v>
       </c>
       <c r="L29" s="14">
         <v>-100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="15">
+        <v>1</v>
+      </c>
+      <c r="K30" s="14">
+        <v>-100</v>
       </c>
       <c r="L30" s="14">
         <v>-100</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
+      </c>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
+        <v>1</v>
+      </c>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="E16" s="14">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
         <v>11</v>
       </c>
       <c r="K16" s="14">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-31.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-42.857142857142</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.692307692307</v>
+        <v>-84.057971014492</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="15">
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" s="15">
         <v>18</v>
       </c>
       <c r="K17" s="14">
+        <v>11.111111111111</v>
+      </c>
+      <c r="L17" s="14">
         <v>0</v>
       </c>
-      <c r="L17" s="14">
-        <v>5.882352941176</v>
-      </c>
       <c r="M17" s="14">
-        <v>63.636363636363</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-64</v>
+        <v>-62.264150943396</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="E18" s="14">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>175</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="15">
         <v>15</v>
       </c>
       <c r="K18" s="14">
-        <v>26.666666666666</v>
+        <v>40</v>
       </c>
       <c r="L18" s="14">
-        <v>5.555555555555</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-24</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.829268292682</v>
+        <v>-76.136363636363</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
         <v>1</v>
       </c>
       <c r="E19" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
         <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I19" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J19" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.157894736842</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L19" s="14">
-        <v>0</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M19" s="14">
-        <v>-8.333333333333</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N19" s="14">
-        <v>-29.787234042553</v>
+        <v>-26.530612244898</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" s="15">
         <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>-62.5</v>
+        <v>-75</v>
       </c>
       <c r="L20" s="14">
-        <v>-72.727272727272</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-57.142857142857</v>
+        <v>-80</v>
       </c>
       <c r="N20" s="14">
-        <v>-96</v>
+        <v>-97.752808988764</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>600</v>
       </c>
       <c r="F21" s="17">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G21" s="17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H21" s="18">
-        <v>10.714285714285</v>
+        <v>37.037037037037</v>
       </c>
       <c r="I21" s="17">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J21" s="17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.888888888888</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.684210526315</v>
+        <v>-11.650485436893</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.684210526315</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.534161490683</v>
+        <v>-74.074074074074</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
-        <v>3</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>2</v>
@@ -1239,19 +1239,19 @@
         <v>-60</v>
       </c>
       <c r="I23" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="15">
         <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>11.764705882352</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M23" s="14">
-        <v>90</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" s="14">
-        <v>-59.183673469387</v>
+        <v>-56</v>
       </c>
       <c r="I24" s="15">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J24" s="15">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K24" s="14">
-        <v>-41.666666666666</v>
+        <v>-40.170940170940</v>
       </c>
       <c r="L24" s="14">
-        <v>-30</v>
+        <v>-29.292929292929</v>
       </c>
       <c r="M24" s="14">
-        <v>-21.25</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>3</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
         <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H25" s="14">
-        <v>-70.967741935483</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="I25" s="15">
         <v>20</v>
       </c>
       <c r="J25" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K25" s="14">
-        <v>-65.517241379310</v>
+        <v>-67.741935483871</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.571428571428</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>3</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="15">
         <v>6</v>
       </c>
-      <c r="E26" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F26" s="15">
-        <v>11</v>
-      </c>
       <c r="G26" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>-45</v>
+        <v>-62.5</v>
       </c>
       <c r="I26" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J26" s="15">
         <v>44</v>
       </c>
       <c r="K26" s="14">
-        <v>-27.272727272727</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="L26" s="14">
-        <v>33.333333333333</v>
+        <v>24</v>
       </c>
       <c r="M26" s="14">
-        <v>-31.914893617021</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
         <v>2</v>
       </c>
       <c r="K28" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -933,14 +933,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
@@ -955,19 +955,19 @@
         <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-31.25</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M16" s="14">
-        <v>-35.294117647058</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.057971014492</v>
+        <v>-86.419753086419</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="14">
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K17" s="14">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M17" s="14">
-        <v>66.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-62.264150943396</v>
+        <v>-64.516129032258</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="15">
+        <v>5</v>
+      </c>
+      <c r="G18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>11</v>
-      </c>
-      <c r="G18" s="15">
-        <v>3</v>
-      </c>
       <c r="H18" s="14">
-        <v>266.666666666667</v>
+        <v>400</v>
       </c>
       <c r="I18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
         <v>15</v>
       </c>
       <c r="K18" s="14">
-        <v>40</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>16.666666666666</v>
+        <v>15</v>
       </c>
       <c r="M18" s="14">
-        <v>-19.230769230769</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.136363636363</v>
+        <v>-74.444444444444</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1066,31 +1066,31 @@
         <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G19" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H19" s="14">
-        <v>21.428571428571</v>
+        <v>30</v>
       </c>
       <c r="I19" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J19" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.692307692307</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="14">
-        <v>-2.702702702702</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M19" s="14">
-        <v>-5.263157894736</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N19" s="14">
-        <v>-26.530612244898</v>
+        <v>-28.301886792452</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,14 +1106,14 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="15">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="15">
         <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="15">
         <v>2</v>
@@ -1125,13 +1125,13 @@
         <v>-75</v>
       </c>
       <c r="L20" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M20" s="14">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.752808988764</v>
+        <v>-97.959183673469</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" s="18">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G21" s="17">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H21" s="18">
-        <v>37.037037037037</v>
+        <v>22.727272727272</v>
       </c>
       <c r="I21" s="17">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J21" s="17">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>2.105263157894</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.650485436893</v>
+        <v>-14.912280701754</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.333333333333</v>
+        <v>-17.796610169491</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.074074074074</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>100</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
         <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="14">
-        <v>17.647058823529</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L23" s="14">
-        <v>-4.761904761904</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M23" s="14">
-        <v>66.666666666666</v>
+        <v>69.230769230769</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-22.222222222222</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F24" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G24" s="15">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H24" s="14">
-        <v>-56</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="I24" s="15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J24" s="15">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="K24" s="14">
-        <v>-40.170940170940</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L24" s="14">
-        <v>-29.292929292929</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.604651162790</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H25" s="14">
-        <v>-74.074074074074</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I25" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="15">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K25" s="14">
-        <v>-67.741935483871</v>
+        <v>-68.656716417910</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.176470588235</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="C26" s="15">
+        <v>3</v>
+      </c>
+      <c r="D26" s="15">
+        <v>6</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
         <v>6</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>-62.5</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J26" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K26" s="14">
-        <v>-29.545454545454</v>
+        <v>-32</v>
       </c>
       <c r="L26" s="14">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M26" s="14">
-        <v>-39.215686274509</v>
+        <v>-44.262295081967</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1437,11 +1437,11 @@
       <c r="F28" s="15">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14">
-        <v>200</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>150</v>
       </c>
       <c r="L28" s="14">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -919,14 +919,14 @@
       <c r="K15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="14">
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,11 +936,11 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
@@ -961,13 +961,13 @@
         <v>-8.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.888888888888</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M16" s="14">
         <v>-38.888888888888</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.419753086419</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-16.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>10</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L17" s="14">
-        <v>4.761904761904</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>37.5</v>
+        <v>31.578947368421</v>
       </c>
       <c r="N17" s="14">
-        <v>-64.516129032258</v>
+        <v>-62.121212121212</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="15">
+        <v>4</v>
+      </c>
+      <c r="G18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>5</v>
-      </c>
-      <c r="G18" s="15">
-        <v>1</v>
-      </c>
       <c r="H18" s="14">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I18" s="15">
         <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>53.333333333333</v>
+        <v>43.75</v>
       </c>
       <c r="L18" s="14">
-        <v>15</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M18" s="14">
         <v>-14.814814814814</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.444444444444</v>
+        <v>-77</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G19" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H19" s="14">
-        <v>30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I19" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J19" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K19" s="14">
-        <v>-5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L19" s="14">
-        <v>-7.317073170731</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.636363636363</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="N19" s="14">
-        <v>-28.301886792452</v>
+        <v>-25.925925925925</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,17 +1100,17 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1119,19 +1119,19 @@
         <v>2</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>-75</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="L20" s="14">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="M20" s="14">
         <v>-81.818181818181</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.959183673469</v>
+        <v>-98.245614035087</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>5</v>
       </c>
       <c r="D21" s="17">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H21" s="18">
-        <v>22.727272727272</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J21" s="17">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="K21" s="18">
-        <v>2.105263157894</v>
+        <v>-4.672897196261</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.912280701754</v>
+        <v>-20.3125</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.796610169491</v>
+        <v>-17.741935483871</v>
       </c>
       <c r="N21" s="18">
-        <v>-75</v>
+        <v>-76.112412177985</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J23" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="14">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L23" s="14">
-        <v>-4.347826086956</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="14">
-        <v>69.230769230769</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14">
-        <v>-23.076923076923</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G24" s="15">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.425531914893</v>
+        <v>-10</v>
       </c>
       <c r="I24" s="15">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J24" s="15">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K24" s="14">
-        <v>-38.461538461538</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.571428571428</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.367346938775</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>4</v>
+      </c>
+      <c r="D25" s="15">
         <v>1</v>
       </c>
-      <c r="D25" s="15">
-        <v>5</v>
-      </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>300</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H25" s="14">
-        <v>-72.727272727272</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" s="15">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" s="14">
-        <v>-68.656716417910</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="L25" s="14">
-        <v>-44.736842105263</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F26" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="15">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-57.142857142857</v>
+        <v>-65</v>
       </c>
       <c r="I26" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J26" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>-32</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="L26" s="14">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="M26" s="14">
-        <v>-44.262295081967</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="14">
+        <v>0</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
         <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>-8.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L16" s="14">
-        <v>-47.619047619047</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-38.888888888888</v>
+        <v>-45</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-88.172043010752</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15">
-        <v>4</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-25</v>
+        <v>1</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>-22.222222222222</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="15">
         <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>4.166666666666</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>3.846153846153</v>
       </c>
       <c r="M17" s="14">
-        <v>31.578947368421</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="14">
-        <v>-62.121212121212</v>
+        <v>-64.473684210526</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
         <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" s="14">
-        <v>43.75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>4.545454545454</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M18" s="14">
-        <v>-14.814814814814</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="N18" s="14">
-        <v>-77</v>
+        <v>-79.487179487179</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
         <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H19" s="14">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J19" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>-14.893617021276</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="N19" s="14">
-        <v>-25.925925925925</v>
+        <v>-24.137931034482</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,17 +1100,17 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="15">
         <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="15">
-        <v>5</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1128,10 +1128,10 @@
         <v>-86.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.245614035087</v>
+        <v>-98.360655737704</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-58.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.692307692307</v>
+        <v>-8</v>
       </c>
       <c r="I21" s="17">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J21" s="17">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.672897196261</v>
+        <v>-5.217391304347</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.3125</v>
+        <v>-19.259259259259</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.741935483871</v>
+        <v>-20.437956204379</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.112412177985</v>
+        <v>-76.857749469214</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>-16.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I23" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="14">
-        <v>20</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L23" s="14">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M23" s="14">
-        <v>71.428571428571</v>
+        <v>73.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D24" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F24" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G24" s="15">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H24" s="14">
-        <v>-10</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I24" s="15">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J24" s="15">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.352941176470</v>
+        <v>-33.566433566433</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.689655172413</v>
+        <v>-22.131147540983</v>
       </c>
       <c r="M24" s="14">
-        <v>-13.207547169811</v>
+        <v>-18.803418803418</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>4</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
         <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H25" s="14">
-        <v>-35.714285714285</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I25" s="15">
         <v>26</v>
       </c>
       <c r="J25" s="15">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K25" s="14">
-        <v>-61.764705882352</v>
+        <v>-62.318840579710</v>
       </c>
       <c r="L25" s="14">
-        <v>-33.333333333333</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15">
         <v>2</v>
       </c>
-      <c r="D26" s="15">
-        <v>8</v>
-      </c>
       <c r="E26" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>-65</v>
+        <v>-62.5</v>
       </c>
       <c r="I26" s="15">
         <v>36</v>
       </c>
       <c r="J26" s="15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K26" s="14">
-        <v>-37.931034482758</v>
+        <v>-40</v>
       </c>
       <c r="L26" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-45.454545454545</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+      <c r="J27" s="15">
+        <v>1</v>
+      </c>
+      <c r="K27" s="14">
+        <v>300</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,29 +1428,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
         <v>150</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -926,48 +926,48 @@
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>-15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M16" s="14">
-        <v>-45</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.172043010752</v>
+        <v>-85.567010309278</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="14">
+        <v>100</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="L17" s="14">
-        <v>3.846153846153</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>28.571428571428</v>
+        <v>26.086956521739</v>
       </c>
       <c r="N17" s="14">
-        <v>-64.473684210526</v>
+        <v>-65.060240963855</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15">
         <v>4</v>
       </c>
-      <c r="G18" s="15">
-        <v>3</v>
-      </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
         <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14">
-        <v>33.333333333333</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L18" s="14">
         <v>4.347826086956</v>
       </c>
       <c r="M18" s="14">
-        <v>-22.580645161290</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.487179487179</v>
+        <v>-81.102362204724</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G19" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J19" s="15">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.333333333333</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.333333333333</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.725490196078</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="N19" s="14">
-        <v>-24.137931034482</v>
+        <v>-19.672131147541</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,32 +1106,32 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+      <c r="F20" s="15">
+        <v>1</v>
       </c>
       <c r="G20" s="15">
         <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="15">
         <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>-81.818181818181</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L20" s="14">
-        <v>-86.666666666666</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="M20" s="14">
-        <v>-83.333333333333</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.360655737704</v>
+        <v>-97.692307692307</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>11</v>
+      </c>
+      <c r="D21" s="17">
         <v>6</v>
       </c>
-      <c r="D21" s="17">
-        <v>8</v>
-      </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G21" s="17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H21" s="18">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="I21" s="17">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.217391304347</v>
+        <v>-0.826446280991</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.259259259259</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.437956204379</v>
+        <v>-19.463087248322</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.857749469214</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>75</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="15">
         <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K23" s="14">
-        <v>23.809523809523</v>
+        <v>4</v>
       </c>
       <c r="L23" s="14">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="M23" s="14">
-        <v>73.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" s="14">
-        <v>-57.142857142857</v>
+        <v>120</v>
       </c>
       <c r="F24" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G24" s="15">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.571428571428</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I24" s="15">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J24" s="15">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.566433566433</v>
+        <v>-28.378378378378</v>
       </c>
       <c r="L24" s="14">
-        <v>-22.131147540983</v>
+        <v>-17.829457364341</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.803418803418</v>
+        <v>-20.895522388059</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H25" s="14">
-        <v>-45.454545454545</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I25" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J25" s="15">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K25" s="14">
-        <v>-62.318840579710</v>
+        <v>-60.563380281690</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.095238095238</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
         <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>250</v>
       </c>
       <c r="F26" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>-62.5</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I26" s="15">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J26" s="15">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K26" s="14">
-        <v>-40</v>
+        <v>-30.645161290322</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>4.878048780487</v>
       </c>
       <c r="M26" s="14">
-        <v>-51.351351351351</v>
+        <v>-45.569620253164</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="14">
-        <v>-36.363636363636</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M16" s="14">
-        <v>-39.130434782608</v>
+        <v>-37.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.567010309278</v>
+        <v>-85.148514851485</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>16</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>26.086956521739</v>
+        <v>19.230769230769</v>
       </c>
       <c r="N17" s="14">
-        <v>-65.060240963855</v>
+        <v>-65.168539325842</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="I18" s="15">
         <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>26.315789473684</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L18" s="14">
         <v>4.347826086956</v>
       </c>
       <c r="M18" s="14">
-        <v>-29.411764705882</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N18" s="14">
-        <v>-81.102362204724</v>
+        <v>-82.481751824817</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H19" s="14">
-        <v>8.333333333333</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I19" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J19" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.921568627450</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L19" s="14">
-        <v>-5.769230769230</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M19" s="14">
-        <v>-7.547169811320</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="N19" s="14">
-        <v>-19.672131147541</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="15">
         <v>3</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>-72.727272727272</v>
+        <v>-75</v>
       </c>
       <c r="L20" s="14">
         <v>-82.352941176470</v>
       </c>
       <c r="M20" s="14">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.692307692307</v>
+        <v>-97.810218978102</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>83.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" s="17">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H21" s="18">
-        <v>-10</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J21" s="17">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.826446280991</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.666666666666</v>
+        <v>-15.231788079470</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.463087248322</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.190476190476</v>
+        <v>-76.029962546816</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,26 +1182,26 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-100</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="14">
         <v>-100</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>3</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>-25</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J23" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K23" s="14">
-        <v>4</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-18.75</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M23" s="14">
-        <v>62.5</v>
+        <v>70.588235294117</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>8</v>
+      </c>
+      <c r="D24" s="15">
         <v>11</v>
       </c>
-      <c r="D24" s="15">
-        <v>5</v>
-      </c>
       <c r="E24" s="14">
-        <v>120</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G24" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H24" s="14">
-        <v>16.129032258064</v>
+        <v>13.793103448275</v>
       </c>
       <c r="I24" s="15">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J24" s="15">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.378378378378</v>
+        <v>-28.930817610062</v>
       </c>
       <c r="L24" s="14">
-        <v>-17.829457364341</v>
+        <v>-16.911764705882</v>
       </c>
       <c r="M24" s="14">
-        <v>-20.895522388059</v>
+        <v>-21.527777777777</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F25" s="15">
         <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J25" s="15">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K25" s="14">
-        <v>-60.563380281690</v>
+        <v>-61.038961038961</v>
       </c>
       <c r="L25" s="14">
-        <v>-39.130434782608</v>
+        <v>-40</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>250</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H26" s="14">
-        <v>-27.777777777777</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J26" s="15">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K26" s="14">
-        <v>-30.645161290322</v>
+        <v>-27.692307692307</v>
       </c>
       <c r="L26" s="14">
-        <v>4.878048780487</v>
+        <v>4.444444444444</v>
       </c>
       <c r="M26" s="14">
-        <v>-45.569620253164</v>
+        <v>-43.373493975903</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>300</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,26 +1434,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="15">
+        <v>1</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
         <v>3</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
         <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-34.782608695652</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.148514851485</v>
+        <v>-84.905660377358</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>10.714285714285</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L17" s="14">
-        <v>3.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M17" s="14">
-        <v>19.230769230769</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="14">
-        <v>-65.168539325842</v>
+        <v>-61.702127659574</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>5</v>
       </c>
       <c r="D18" s="15">
         <v>7</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-90.909090909090</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-7.692307692307</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L18" s="14">
-        <v>4.347826086956</v>
+        <v>26.086956521739</v>
       </c>
       <c r="M18" s="14">
-        <v>-31.428571428571</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.481751824817</v>
+        <v>-79.861111111111</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
+        <v>18</v>
+      </c>
+      <c r="G19" s="15">
         <v>16</v>
       </c>
-      <c r="G19" s="15">
-        <v>17</v>
-      </c>
       <c r="H19" s="14">
-        <v>-5.882352941176</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J19" s="15">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.263157894736</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-3.571428571428</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="M19" s="14">
-        <v>-12.903225806451</v>
+        <v>-13.235294117647</v>
       </c>
       <c r="N19" s="14">
-        <v>-15.625</v>
+        <v>-11.940298507462</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I20" s="15">
         <v>4</v>
       </c>
-      <c r="H20" s="14">
-        <v>-75</v>
-      </c>
-      <c r="I20" s="15">
-        <v>3</v>
-      </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14">
-        <v>-75</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="L20" s="14">
-        <v>-82.352941176470</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="M20" s="14">
-        <v>-80</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.810218978102</v>
+        <v>-97.183098591549</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-57.894736842105</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G21" s="17">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.333333333333</v>
+        <v>-16.326530612244</v>
       </c>
       <c r="I21" s="17">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.571428571428</v>
+        <v>-7.051282051282</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.231788079470</v>
+        <v>-11.585365853658</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.951219512195</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.029962546816</v>
+        <v>-74.060822898032</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
+        <v>200</v>
+      </c>
+      <c r="I22" s="15">
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M22" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="14">
-        <v>-41.666666666666</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I23" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J23" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" s="14">
-        <v>-3.333333333333</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L23" s="14">
-        <v>-17.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="14">
-        <v>70.588235294117</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
+        <v>30</v>
+      </c>
+      <c r="G24" s="15">
         <v>33</v>
       </c>
-      <c r="G24" s="15">
-        <v>29</v>
-      </c>
       <c r="H24" s="14">
-        <v>13.793103448275</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I24" s="15">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J24" s="15">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.930817610062</v>
+        <v>-28.402366863905</v>
       </c>
       <c r="L24" s="14">
-        <v>-16.911764705882</v>
+        <v>-14.788732394366</v>
       </c>
       <c r="M24" s="14">
-        <v>-21.527777777777</v>
+        <v>-19.867549668874</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
         <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>-83.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="15">
         <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>-20</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K25" s="14">
-        <v>-61.038961038961</v>
+        <v>-59.036144578313</v>
       </c>
       <c r="L25" s="14">
-        <v>-40</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F26" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I26" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>-27.692307692307</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L26" s="14">
-        <v>4.444444444444</v>
+        <v>10.869565217391</v>
       </c>
       <c r="M26" s="14">
-        <v>-43.373493975903</v>
+        <v>-42.045454545454</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-076pct.xlsx
+++ b/data/source/weekly/cs-en-us-076pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -904,11 +904,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,38 +936,38 @@
       <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
         <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.461538461538</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.333333333333</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.905660377358</v>
+        <v>-84.955752212389</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>400</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K17" s="14">
-        <v>24.137931034482</v>
+        <v>15.625</v>
       </c>
       <c r="L17" s="14">
-        <v>9.090909090909</v>
+        <v>8.823529411764</v>
       </c>
       <c r="M17" s="14">
-        <v>28.571428571428</v>
+        <v>15.625</v>
       </c>
       <c r="N17" s="14">
-        <v>-61.702127659574</v>
+        <v>-63.366336633663</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-28.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>-64.705882352941</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="14">
-        <v>-12.121212121212</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>26.086956521739</v>
+        <v>20</v>
       </c>
       <c r="M18" s="14">
-        <v>-23.684210526315</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.861111111111</v>
+        <v>-80.132450331125</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1069,42 +1069,42 @@
         <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="I19" s="15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14">
-        <v>-6.349206349206</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="M19" s="14">
-        <v>-13.235294117647</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N19" s="14">
-        <v>-11.940298507462</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>5</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-80</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
@@ -1128,10 +1128,10 @@
         <v>-76.470588235294</v>
       </c>
       <c r="M20" s="14">
-        <v>-73.333333333333</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.183098591549</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F21" s="17">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G21" s="17">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.326530612244</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I21" s="17">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.051282051282</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.585365853658</v>
+        <v>-12.138728323699</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.142857142857</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.060822898032</v>
+        <v>-74.496644295302</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>21</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="15">
         <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H23" s="14">
-        <v>-27.272727272727</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I23" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K23" s="14">
-        <v>3.225806451612</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="L23" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M23" s="14">
-        <v>77.777777777777</v>
+        <v>78.947368421052</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F24" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G24" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H24" s="14">
-        <v>-9.090909090909</v>
+        <v>24.137931034482</v>
       </c>
       <c r="I24" s="15">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="J24" s="15">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.402366863905</v>
+        <v>-24.418604651162</v>
       </c>
       <c r="L24" s="14">
-        <v>-14.788732394366</v>
+        <v>-15.032679738562</v>
       </c>
       <c r="M24" s="14">
-        <v>-19.867549668874</v>
+        <v>-18.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
-      </c>
-      <c r="D25" s="15">
-        <v>6</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-33.333333333333</v>
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" s="14">
-        <v>-46.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J25" s="15">
         <v>83</v>
       </c>
       <c r="K25" s="14">
-        <v>-59.036144578313</v>
+        <v>-53.012048192771</v>
       </c>
       <c r="L25" s="14">
-        <v>-38.181818181818</v>
+        <v>-41.791044776119</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
-      </c>
-      <c r="D26" s="15">
-        <v>1</v>
-      </c>
-      <c r="E26" s="14">
-        <v>300</v>
+        <v>6</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J26" s="15">
         <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>-22.727272727272</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L26" s="14">
-        <v>10.869565217391</v>
+        <v>20.833333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-42.045454545454</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
